--- a/data/trans_orig/IQ14-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud</t>
+          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,27 +721,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,02</t>
+          <t>1,18; 3,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,9</t>
+          <t>1,42; 5,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,3</t>
+          <t>3,38; 9,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,24</t>
+          <t>1,73; 9,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,09</t>
+          <t>1,0; 7,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 22,06</t>
+          <t>2,3; 21,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,31</t>
+          <t>1,84; 7,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,61</t>
+          <t>1,28; 4,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,94</t>
+          <t>1,84; 5,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,38</t>
+          <t>3,64; 13,25</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,59</t>
+          <t>1,0; 2,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,07</t>
+          <t>1,59; 3,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,34</t>
+          <t>1,23; 5,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,18</t>
+          <t>2,23; 5,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,32 +886,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,49</t>
+          <t>1,21; 3,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,21</t>
+          <t>2,6; 6,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,14</t>
+          <t>1,72; 4,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,74</t>
+          <t>1,56; 2,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,99</t>
+          <t>1,35; 3,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,31</t>
+          <t>2,47; 5,36</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,38</t>
+          <t>1,16; 2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,22 +1006,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,09</t>
+          <t>1,85; 5,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,07</t>
+          <t>1,7; 4,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,23</t>
+          <t>1,2; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,19</t>
+          <t>1,1; 6,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 9,04</t>
+          <t>2,7; 8,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,88</t>
+          <t>1,29; 2,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,79</t>
+          <t>1,47; 4,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,76</t>
+          <t>1,85; 3,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,8</t>
+          <t>2,52; 6,9</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,87</t>
+          <t>1,64; 4,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,57</t>
+          <t>2,09; 5,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,13</t>
+          <t>1,82; 3,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,92</t>
+          <t>3,24; 5,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,23</t>
+          <t>1,58; 4,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,78</t>
+          <t>1,65; 3,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,37</t>
+          <t>1,32; 2,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,24</t>
+          <t>2,68; 5,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,66</t>
+          <t>1,9; 3,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,67</t>
+          <t>1,99; 3,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,61</t>
+          <t>1,73; 2,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,04</t>
+          <t>3,23; 5,1</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,59</t>
+          <t>1,32; 11,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,33</t>
+          <t>1,56; 4,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,58</t>
+          <t>1,99; 9,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,5</t>
+          <t>2,4; 4,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,45</t>
+          <t>2,1; 4,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,1</t>
+          <t>1,59; 4,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,88</t>
+          <t>1,15; 1,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,98</t>
+          <t>4,13; 6,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,63</t>
+          <t>2,14; 6,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,62</t>
+          <t>1,87; 3,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,87</t>
+          <t>1,64; 6,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,35</t>
+          <t>3,42; 5,35</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 11,43</t>
+          <t>1,8; 11,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,52</t>
+          <t>2,24; 5,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,81</t>
+          <t>1,39; 3,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 8,56</t>
+          <t>1,7; 8,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 18,22</t>
+          <t>2,57; 18,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,0</t>
+          <t>1,87; 5,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,04</t>
+          <t>1,71; 6,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,85</t>
+          <t>1,13; 5,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,88</t>
+          <t>3,13; 12,21</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,08</t>
+          <t>1,99; 4,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,24</t>
+          <t>2,02; 3,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,85</t>
+          <t>2,29; 3,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,7</t>
+          <t>3,18; 4,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,72</t>
+          <t>2,14; 3,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,41</t>
+          <t>2,01; 3,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,31</t>
+          <t>1,55; 2,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,04</t>
+          <t>4,07; 6,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,46</t>
+          <t>2,25; 3,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,09</t>
+          <t>2,15; 3,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,98</t>
+          <t>2,01; 2,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,75</t>
+          <t>3,91; 5,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,27 +721,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,19</t>
+          <t>1,17; 2,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,87</t>
+          <t>1,87; 6,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,56</t>
+          <t>3,33; 9,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,01</t>
+          <t>1,76; 9,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,07</t>
+          <t>1,0; 7,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 21,48</t>
+          <t>2,58; 22,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,01</t>
+          <t>1,81; 6,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,71</t>
+          <t>1,36; 4,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,33</t>
+          <t>1,78; 5,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,25</t>
+          <t>3,78; 12,31</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,08</t>
+          <t>1,58; 3,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,12</t>
+          <t>1,47; 5,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,44</t>
+          <t>2,06; 5,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,32 +886,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,65</t>
+          <t>1,21; 3,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,48</t>
+          <t>2,54; 6,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,06</t>
+          <t>1,75; 4,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,71</t>
+          <t>1,54; 2,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,08</t>
+          <t>1,28; 2,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,36</t>
+          <t>2,51; 5,26</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,48</t>
+          <t>1,17; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,36</t>
+          <t>1,75; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,42 +1016,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,21</t>
+          <t>1,0; 4,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,13</t>
+          <t>1,27; 6,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,03</t>
+          <t>1,42; 3,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,53</t>
+          <t>2,97; 8,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,9</t>
+          <t>1,29; 2,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,73</t>
+          <t>1,48; 5,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,94</t>
+          <t>1,77; 3,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,9</t>
+          <t>2,57; 7,04</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,18</t>
+          <t>1,57; 3,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,34</t>
+          <t>2,14; 5,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,18</t>
+          <t>1,81; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,83</t>
+          <t>3,3; 5,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,16</t>
+          <t>1,6; 4,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,59</t>
+          <t>1,69; 3,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,36</t>
+          <t>1,31; 2,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,13</t>
+          <t>2,78; 5,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,61</t>
+          <t>1,82; 3,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,85</t>
+          <t>1,98; 3,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,6</t>
+          <t>1,74; 2,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,1</t>
+          <t>3,19; 5,01</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,43</t>
+          <t>1,0; 11,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,09</t>
+          <t>1,7; 4,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,58</t>
+          <t>2,03; 9,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,63</t>
+          <t>2,41; 4,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,5</t>
+          <t>1,92; 4,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,03</t>
+          <t>1,62; 3,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,86</t>
+          <t>1,15; 1,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,9</t>
+          <t>4,09; 6,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,69</t>
+          <t>2,04; 6,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,62</t>
+          <t>1,8; 3,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,18</t>
+          <t>1,58; 5,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,35</t>
+          <t>3,42; 5,31</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 11,37</t>
+          <t>1,8; 11,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,52</t>
+          <t>2,22; 5,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,69</t>
+          <t>1,4; 3,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,6</t>
+          <t>1,69; 8,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 18,22</t>
+          <t>2,1; 18,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,89</t>
+          <t>1,93; 6,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,95</t>
+          <t>1,73; 7,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,18</t>
+          <t>1,13; 5,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 12,21</t>
+          <t>3,0; 12,09</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,15</t>
+          <t>2,04; 4,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,31</t>
+          <t>2,03; 3,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,81</t>
+          <t>2,24; 3,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,63</t>
+          <t>3,25; 4,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,62</t>
+          <t>2,13; 3,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,44</t>
+          <t>1,98; 3,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,29</t>
+          <t>1,56; 2,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,9</t>
+          <t>4,02; 6,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,45</t>
+          <t>2,26; 3,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,14</t>
+          <t>2,14; 3,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,95</t>
+          <t>2,03; 2,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 5,66</t>
+          <t>3,85; 5,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Clase-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo medio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,06</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,24</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,81</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,76</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,55</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>6,44</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1,66; 9,24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 7,09</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 3,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2,59; 21,93</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1,0; 5,6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 2,98</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 6,21</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3,33; 9,03</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,76; 9,26</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,08</t>
+          <t>1,17; 3,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,0</t>
+          <t>1,78; 5,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 22,06</t>
+          <t>3,3; 9,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,98</t>
+          <t>1,82; 7,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,8</t>
+          <t>1,35; 4,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,1</t>
+          <t>1,79; 4,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 12,31</t>
+          <t>3,82; 12,06</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,45</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,03</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,58</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,22</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,68</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,57</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,4</t>
+          <t>2,14; 5,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,17</t>
+          <t>1,0; 2,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1,2; 3,49</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2,52; 6,05</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 2,59</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,6; 3,07</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>1,0; 2,0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 5,39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,06; 5,27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 2,0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 3,61</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,17</t>
+          <t>1,22; 5,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,06</t>
+          <t>1,74; 4,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,76</t>
+          <t>1,53; 2,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,98</t>
+          <t>1,33; 2,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,26</t>
+          <t>2,47; 5,16</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,84</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,05</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,62</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,39</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,09</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,84</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>4,3</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,4</t>
+          <t>1,0; 4,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>1,29; 7,19</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1,27; 3,03</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3,41; 9,16</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,16; 2,38</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>1,0; 5,66</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,75; 5,49</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,7; 4,82</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 4,22</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 6,85</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,06</t>
+          <t>1,7; 5,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,65</t>
+          <t>1,73; 4,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,87</t>
+          <t>1,36; 2,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,05</t>
+          <t>1,44; 4,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,82</t>
+          <t>1,8; 3,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,04</t>
+          <t>2,65; 7,05</t>
         </is>
       </c>
     </row>
@@ -1073,44 +1073,44 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,78</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>3,43</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,25</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4,51</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2,52</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,73</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>2,64</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>4,06</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,88</t>
+          <t>1,66; 4,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,4</t>
+          <t>1,68; 3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,16</t>
+          <t>1,34; 2,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,77</t>
+          <t>2,67; 5,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,41</t>
+          <t>1,62; 3,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,75</t>
+          <t>2,25; 5,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,29</t>
+          <t>1,81; 3,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,14</t>
+          <t>3,23; 5,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,58</t>
+          <t>1,83; 3,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,77</t>
+          <t>2,03; 3,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,74</t>
+          <t>1,73; 2,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,01</t>
+          <t>3,26; 5,14</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,87</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,28</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,99</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,65</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>4,85</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 11,53</t>
+          <t>2,03; 4,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,33</t>
+          <t>1,69; 4,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,5</t>
+          <t>1,12; 1,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,53</t>
+          <t>4,11; 6,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,39</t>
+          <t>1,32; 11,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,95</t>
+          <t>1,64; 4,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,87</t>
+          <t>2,0; 9,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 6,83</t>
+          <t>2,39; 4,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,37</t>
+          <t>2,09; 6,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,6</t>
+          <t>1,88; 3,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,96</t>
+          <t>1,59; 5,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,31</t>
+          <t>3,4; 5,33</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,25</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,78</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9,14</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4,46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,29</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>6,11</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 11,4</t>
+          <t>1,4; 3,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>1,68; 8,56</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 7,0</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3,72; 18,13</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1,8; 11,43</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>1,0; 2,0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 5,31</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 3,81</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,69; 8,06</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 7,0</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 18,22</t>
+          <t>2,28; 5,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,65</t>
+          <t>1,94; 6,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,32</t>
+          <t>1,72; 7,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,33</t>
+          <t>1,0; 4,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,09</t>
+          <t>3,35; 13,11</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,54</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5,22</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2,73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,57</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,86</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,54</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,58</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,08</t>
+          <t>2,25; 3,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,32</t>
+          <t>2,0; 3,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,77</t>
+          <t>1,56; 2,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,72</t>
+          <t>4,19; 7,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,67</t>
+          <t>1,9; 4,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,55</t>
+          <t>2,02; 3,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,29</t>
+          <t>2,18; 3,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,89</t>
+          <t>3,17; 4,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,49</t>
+          <t>2,24; 3,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,15</t>
+          <t>2,11; 3,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,98</t>
+          <t>2,0; 2,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,68</t>
+          <t>3,93; 5,73</t>
         </is>
       </c>
     </row>
